--- a/academias/Programación - Estadisticos 20222.xlsx
+++ b/academias/Programación - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="32">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,7 +47,7 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
@@ -69,6 +68,33 @@
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>DESARROLLA APLICACIONES QUE SE EJECUTAN EN EL SERVIDOR</t>
+  </si>
+  <si>
+    <t>DESARROLLA APLICACIONES MÓVILES PARA ANDROID</t>
+  </si>
+  <si>
+    <t>APLICA ESTRUCTURAS DE DATOS CON UN LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>DESARROLLA APLICACIONES QUE SE EJECUTAN EN EL CLIENTE</t>
+  </si>
+  <si>
+    <t>APLICA ESTRUCTURAS DE CONTROL CON UN LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>DESARROLLA APLICACIONES MÓVILES PARA IOS</t>
+  </si>
+  <si>
+    <t>CONSTRUYE ALGORITMOS PARA LA SOLUCIÓN DE PROBLEMAS</t>
+  </si>
+  <si>
+    <t>CONSTRUYE PÁGINAS WEB</t>
+  </si>
+  <si>
     <t>4APV</t>
   </si>
   <si>
@@ -85,30 +111,6 @@
   </si>
   <si>
     <t>6APM</t>
-  </si>
-  <si>
-    <t>DESARROLLA APLICACIONES QUE SE EJECUTAN EN EL SERVIDOR</t>
-  </si>
-  <si>
-    <t>DESARROLLA APLICACIONES MÓVILES PARA ANDROID</t>
-  </si>
-  <si>
-    <t>APLICA ESTRUCTURAS DE DATOS CON UN LENGUAJE DE PROGRAMACIÓN</t>
-  </si>
-  <si>
-    <t>DESARROLLA APLICACIONES QUE SE EJECUTAN EN EL CLIENTE</t>
-  </si>
-  <si>
-    <t>APLICA ESTRUCTURAS DE CONTROL CON UN LENGUAJE DE PROGRAMACIÓN</t>
-  </si>
-  <si>
-    <t>DESARROLLA APLICACIONES MÓVILES PARA IOS</t>
-  </si>
-  <si>
-    <t>CONSTRUYE ALGORITMOS PARA LA SOLUCIÓN DE PROBLEMAS</t>
-  </si>
-  <si>
-    <t>CONSTRUYE PÁGINAS WEB</t>
   </si>
 </sst>
 </file>
@@ -472,11 +474,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -522,10 +524,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -557,10 +559,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>17</v>
@@ -589,31 +591,25 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>87.18000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>12.82</v>
+        <v>21.4</v>
       </c>
       <c r="I4" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -630,25 +626,25 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>80</v>
+        <v>87.2</v>
       </c>
       <c r="H5" s="1">
-        <v>20</v>
+        <v>12.8</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -662,28 +658,28 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H6" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -694,31 +690,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7">
-        <v>39</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
       <c r="F7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>56.41</v>
+        <v>76</v>
       </c>
       <c r="H7" s="1">
-        <v>43.59</v>
+        <v>24</v>
       </c>
       <c r="I7" s="2">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -729,31 +725,25 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
-        <v>92.86</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>7.14</v>
+        <v>18.1</v>
       </c>
       <c r="I8" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -773,22 +763,22 @@
         <v>28</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>100</v>
+        <v>56.4</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>43.6</v>
       </c>
       <c r="I9" s="2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -799,31 +789,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E10">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>94.87</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>5.13</v>
+        <v>7.1</v>
       </c>
       <c r="I10" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -834,31 +824,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11">
         <v>20</v>
       </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11">
-        <v>30</v>
-      </c>
       <c r="E11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -869,31 +859,25 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D12">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1">
-        <v>100</v>
+        <v>78.2</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>21.8</v>
       </c>
       <c r="I12" s="2">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -904,31 +888,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I13" s="2">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -939,31 +923,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1">
-        <v>96.43000000000001</v>
+        <v>60</v>
       </c>
       <c r="H14" s="1">
-        <v>3.57</v>
+        <v>40</v>
       </c>
       <c r="I14" s="2">
-        <v>8.300000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -974,31 +958,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15">
-        <v>25</v>
-      </c>
       <c r="E15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1009,31 +993,25 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D16">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1">
-        <v>95</v>
+        <v>83.7</v>
       </c>
       <c r="H16" s="1">
-        <v>5</v>
+        <v>16.3</v>
       </c>
       <c r="I16" s="2">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1044,36 +1022,263 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17">
+        <v>28</v>
+      </c>
+      <c r="E17">
+        <v>28</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18">
+        <v>28</v>
+      </c>
+      <c r="E18">
+        <v>27</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="H18" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19">
+        <v>25</v>
+      </c>
+      <c r="E19">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="F19">
+        <v>9</v>
+      </c>
+      <c r="G19" s="1">
+        <v>64</v>
+      </c>
+      <c r="H19" s="1">
+        <v>36</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20">
         <v>20</v>
       </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17">
+      <c r="E20">
+        <v>19</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>95</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21">
+        <v>101</v>
+      </c>
+      <c r="E21">
+        <v>90</v>
+      </c>
+      <c r="F21">
+        <v>11</v>
+      </c>
+      <c r="G21" s="1">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="H21" s="1">
+        <v>10.9</v>
+      </c>
+      <c r="I21" s="2">
+        <v>8</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22">
         <v>30</v>
       </c>
-      <c r="E17">
+      <c r="E22">
         <v>29</v>
       </c>
-      <c r="F17">
+      <c r="F22">
         <v>1</v>
       </c>
-      <c r="G17" s="1">
-        <v>96.67</v>
-      </c>
-      <c r="H17" s="1">
-        <v>3.33</v>
-      </c>
-      <c r="I17" s="2">
+      <c r="G22" s="1">
+        <v>96.7</v>
+      </c>
+      <c r="H22" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="I22" s="2">
         <v>7.5</v>
       </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>96.7</v>
+      </c>
+      <c r="H23" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="I23" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24">
+        <v>440</v>
+      </c>
+      <c r="E24">
+        <v>369</v>
+      </c>
+      <c r="F24">
+        <v>71</v>
+      </c>
+      <c r="G24" s="1">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="H24" s="1">
+        <v>16.1</v>
+      </c>
+      <c r="I24" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1084,11 +1289,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1134,31 +1339,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>25</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>36</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.1</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1166,63 +1374,63 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>17</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7.7</v>
       </c>
       <c r="J3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>21.4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1233,28 +1441,31 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>87.2</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>12.8</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.9</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1262,95 +1473,98 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.1</v>
       </c>
       <c r="J6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7">
-        <v>39</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
       <c r="F7">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.3</v>
       </c>
       <c r="J7">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>18.1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.4</v>
       </c>
       <c r="J8">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1364,892 +1578,522 @@
         <v>28</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>43.6</v>
+      </c>
+      <c r="I9" s="2">
+        <v>6.6</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>7.1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.5</v>
       </c>
       <c r="J10">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11">
         <v>20</v>
       </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11">
-        <v>30</v>
-      </c>
       <c r="E11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.3</v>
       </c>
       <c r="J11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D12">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F12">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>78.2</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>21.8</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.1</v>
       </c>
       <c r="J12">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F13">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>5.1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.4</v>
       </c>
       <c r="J13">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>40</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6.1</v>
       </c>
       <c r="J14">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15">
-        <v>25</v>
-      </c>
       <c r="E15">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8.4</v>
       </c>
       <c r="J15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D16">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>83.7</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>16.3</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.3</v>
       </c>
       <c r="J16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17">
+        <v>28</v>
+      </c>
+      <c r="E17">
+        <v>28</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18">
+        <v>28</v>
+      </c>
+      <c r="E18">
+        <v>27</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="H18" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19">
+        <v>25</v>
+      </c>
+      <c r="E19">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="F19">
+        <v>9</v>
+      </c>
+      <c r="G19" s="1">
+        <v>64</v>
+      </c>
+      <c r="H19" s="1">
+        <v>36</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20">
         <v>20</v>
       </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17">
+      <c r="E20">
+        <v>19</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>95</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21">
+        <v>101</v>
+      </c>
+      <c r="E21">
+        <v>90</v>
+      </c>
+      <c r="F21">
+        <v>11</v>
+      </c>
+      <c r="G21" s="1">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="H21" s="1">
+        <v>10.9</v>
+      </c>
+      <c r="I21" s="2">
+        <v>8</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22">
         <v>30</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
+      <c r="E22">
+        <v>29</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>96.7</v>
+      </c>
+      <c r="H22" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23">
         <v>30</v>
       </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>100</v>
-      </c>
-      <c r="J17">
-        <v>30</v>
-      </c>
-      <c r="K17" s="1">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="E23">
+        <v>29</v>
+      </c>
+      <c r="F23">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="G23" s="1">
+        <v>96.7</v>
+      </c>
+      <c r="H23" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="I23" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2">
-        <v>25</v>
-      </c>
-      <c r="E2">
-        <v>16</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1">
-        <v>64</v>
-      </c>
-      <c r="H2" s="1">
-        <v>36</v>
-      </c>
-      <c r="I2" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3">
-        <v>17</v>
-      </c>
-      <c r="E3">
-        <v>17</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1">
-        <v>100</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4">
-        <v>39</v>
-      </c>
-      <c r="E4">
-        <v>34</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4" s="1">
-        <v>87.18000000000001</v>
-      </c>
-      <c r="H4" s="1">
-        <v>12.82</v>
-      </c>
-      <c r="I4" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5">
-        <v>30</v>
-      </c>
-      <c r="E5">
-        <v>24</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5" s="1">
-        <v>80</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>25</v>
-      </c>
-      <c r="E6">
-        <v>19</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6" s="1">
-        <v>76</v>
-      </c>
-      <c r="H6" s="1">
-        <v>24</v>
-      </c>
-      <c r="I6" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7">
-        <v>39</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>17</v>
-      </c>
-      <c r="G7" s="1">
-        <v>56.41</v>
-      </c>
-      <c r="H7" s="1">
-        <v>43.59</v>
-      </c>
-      <c r="I7" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8">
-        <v>28</v>
-      </c>
-      <c r="E8">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>92.86</v>
-      </c>
-      <c r="H8" s="1">
-        <v>7.14</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="D24">
+        <v>440</v>
+      </c>
+      <c r="E24">
+        <v>369</v>
+      </c>
+      <c r="F24">
+        <v>71</v>
+      </c>
+      <c r="G24" s="1">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="H24" s="1">
+        <v>16.1</v>
+      </c>
+      <c r="I24" s="2">
         <v>7.5</v>
       </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9">
-        <v>20</v>
-      </c>
-      <c r="E9">
-        <v>20</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>100</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10">
-        <v>39</v>
-      </c>
-      <c r="E10">
-        <v>37</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10" s="1">
-        <v>94.87</v>
-      </c>
-      <c r="H10" s="1">
-        <v>5.13</v>
-      </c>
-      <c r="I10" s="2">
-        <v>7.4</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11">
-        <v>30</v>
-      </c>
-      <c r="E11">
-        <v>18</v>
-      </c>
-      <c r="F11">
-        <v>12</v>
-      </c>
-      <c r="G11" s="1">
-        <v>60</v>
-      </c>
-      <c r="H11" s="1">
-        <v>40</v>
-      </c>
-      <c r="I11" s="2">
-        <v>6.1</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12">
-        <v>17</v>
-      </c>
-      <c r="E12">
-        <v>17</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1">
-        <v>100</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
-        <v>8.4</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13">
-        <v>28</v>
-      </c>
-      <c r="E13">
-        <v>28</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>100</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14">
-        <v>28</v>
-      </c>
-      <c r="E14">
-        <v>27</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1">
-        <v>96.43000000000001</v>
-      </c>
-      <c r="H14" s="1">
-        <v>3.57</v>
-      </c>
-      <c r="I14" s="2">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15">
-        <v>25</v>
-      </c>
-      <c r="E15">
-        <v>16</v>
-      </c>
-      <c r="F15">
-        <v>9</v>
-      </c>
-      <c r="G15" s="1">
-        <v>64</v>
-      </c>
-      <c r="H15" s="1">
-        <v>36</v>
-      </c>
-      <c r="I15" s="2">
-        <v>6.8</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16">
-        <v>20</v>
-      </c>
-      <c r="E16">
-        <v>19</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1">
-        <v>95</v>
-      </c>
-      <c r="H16" s="1">
-        <v>5</v>
-      </c>
-      <c r="I16" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17">
-        <v>30</v>
-      </c>
-      <c r="E17">
-        <v>29</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>96.67</v>
-      </c>
-      <c r="H17" s="1">
-        <v>3.33</v>
-      </c>
-      <c r="I17" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Programación - Estadisticos 20222.xlsx
+++ b/academias/Programación - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="33">
   <si>
     <t>Docente</t>
   </si>
@@ -68,15 +68,15 @@
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>DESARROLLA APLICACIONES QUE SE EJECUTAN EN EL SERVIDOR</t>
   </si>
   <si>
     <t>DESARROLLA APLICACIONES MÓVILES PARA ANDROID</t>
   </si>
   <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
     <t>APLICA ESTRUCTURAS DE DATOS CON UN LENGUAJE DE PROGRAMACIÓN</t>
   </si>
   <si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>CONSTRUYE PÁGINAS WEB</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>4APV</t>
@@ -478,7 +481,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -524,10 +527,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -559,10 +562,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>17</v>
@@ -593,6 +596,9 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
       <c r="D4">
         <v>42</v>
       </c>
@@ -626,7 +632,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>39</v>
@@ -661,7 +667,7 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -696,7 +702,7 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>25</v>
@@ -727,6 +733,9 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
       <c r="D8">
         <v>94</v>
       </c>
@@ -760,7 +769,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9">
         <v>39</v>
@@ -795,7 +804,7 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10">
         <v>28</v>
@@ -830,7 +839,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11">
         <v>20</v>
@@ -861,6 +870,9 @@
       <c r="A12" t="s">
         <v>13</v>
       </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
       <c r="D12">
         <v>87</v>
       </c>
@@ -894,7 +906,7 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>39</v>
@@ -929,7 +941,7 @@
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14">
         <v>30</v>
@@ -964,7 +976,7 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>17</v>
@@ -995,6 +1007,9 @@
       <c r="A16" t="s">
         <v>14</v>
       </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
       <c r="D16">
         <v>86</v>
       </c>
@@ -1028,7 +1043,7 @@
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17">
         <v>28</v>
@@ -1060,10 +1075,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18">
         <v>28</v>
@@ -1098,7 +1113,7 @@
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19">
         <v>25</v>
@@ -1130,10 +1145,10 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20">
         <v>20</v>
@@ -1164,6 +1179,9 @@
       <c r="A21" t="s">
         <v>15</v>
       </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
       <c r="D21">
         <v>101</v>
       </c>
@@ -1197,7 +1215,7 @@
         <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22">
         <v>30</v>
@@ -1228,6 +1246,9 @@
       <c r="A23" t="s">
         <v>16</v>
       </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
       <c r="D23">
         <v>30</v>
       </c>
@@ -1254,8 +1275,8 @@
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>17</v>
+      <c r="B24" t="s">
+        <v>26</v>
       </c>
       <c r="D24">
         <v>440</v>
@@ -1339,10 +1360,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -1374,10 +1395,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>17</v>
@@ -1408,6 +1429,9 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
       <c r="D4">
         <v>42</v>
       </c>
@@ -1441,7 +1465,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>39</v>
@@ -1476,7 +1500,7 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -1511,7 +1535,7 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>25</v>
@@ -1542,6 +1566,9 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
       <c r="D8">
         <v>94</v>
       </c>
@@ -1575,7 +1602,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9">
         <v>39</v>
@@ -1610,7 +1637,7 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10">
         <v>28</v>
@@ -1645,7 +1672,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11">
         <v>20</v>
@@ -1676,6 +1703,9 @@
       <c r="A12" t="s">
         <v>13</v>
       </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
       <c r="D12">
         <v>87</v>
       </c>
@@ -1709,7 +1739,7 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>39</v>
@@ -1744,7 +1774,7 @@
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14">
         <v>30</v>
@@ -1779,7 +1809,7 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>17</v>
@@ -1810,6 +1840,9 @@
       <c r="A16" t="s">
         <v>14</v>
       </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
       <c r="D16">
         <v>86</v>
       </c>
@@ -1843,7 +1876,7 @@
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17">
         <v>28</v>
@@ -1875,10 +1908,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18">
         <v>28</v>
@@ -1913,7 +1946,7 @@
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19">
         <v>25</v>
@@ -1945,10 +1978,10 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20">
         <v>20</v>
@@ -1979,6 +2012,9 @@
       <c r="A21" t="s">
         <v>15</v>
       </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
       <c r="D21">
         <v>101</v>
       </c>
@@ -2012,7 +2048,7 @@
         <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22">
         <v>30</v>
@@ -2043,6 +2079,9 @@
       <c r="A23" t="s">
         <v>16</v>
       </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
       <c r="D23">
         <v>30</v>
       </c>
@@ -2069,8 +2108,8 @@
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>17</v>
+      <c r="B24" t="s">
+        <v>26</v>
       </c>
       <c r="D24">
         <v>440</v>

--- a/academias/Programación - Estadisticos 20222.xlsx
+++ b/academias/Programación - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="33">
   <si>
     <t>Docente</t>
   </si>
@@ -1369,6 +1370,839 @@
         <v>25</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3">
+        <v>17</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>42</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>42</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>42</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>39</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>39</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>39</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>30</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>25</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>94</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>94</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>94</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9">
+        <v>39</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>39</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>39</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10">
+        <v>28</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>28</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>28</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>87</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>87</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>87</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>39</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>39</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>39</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>30</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>30</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15">
+        <v>17</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>17</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>17</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16">
+        <v>86</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>86</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>86</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17">
+        <v>28</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>28</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>100</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>28</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18">
+        <v>28</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>28</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>28</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19">
+        <v>25</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>25</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>25</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20">
+        <v>20</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>20</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>100</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>20</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21">
+        <v>101</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>101</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>100</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>101</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22">
+        <v>30</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>30</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>100</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>30</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>30</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>100</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24">
+        <v>440</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>440</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>100</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>440</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2">
+        <v>25</v>
+      </c>
+      <c r="E2">
         <v>16</v>
       </c>
       <c r="F2">

--- a/academias/Programación - Estadisticos 20222.xlsx
+++ b/academias/Programación - Estadisticos 20222.xlsx
@@ -1370,25 +1370,25 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1405,25 +1405,25 @@
         <v>17</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1437,25 +1437,25 @@
         <v>42</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F4">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1472,25 +1472,25 @@
         <v>39</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>15.4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1507,25 +1507,25 @@
         <v>30</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1542,25 +1542,25 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1574,25 +1574,25 @@
         <v>94</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F8">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>78.7</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>21.3</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J8">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1609,25 +1609,25 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>43.6</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J9">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1644,25 +1644,25 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J10">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1679,25 +1679,25 @@
         <v>20</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1711,25 +1711,25 @@
         <v>87</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F12">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>24.1</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J12">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1781,25 +1781,25 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>36.7</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J14">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1816,25 +1816,25 @@
         <v>17</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1848,25 +1848,25 @@
         <v>86</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F16">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>41.9</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>58.1</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="J16">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1883,25 +1883,25 @@
         <v>28</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F17">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J17">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1918,25 +1918,25 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F18">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J18">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1953,25 +1953,25 @@
         <v>25</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J19">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1988,25 +1988,25 @@
         <v>20</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J20">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2020,25 +2020,25 @@
         <v>101</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="F21">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>13.9</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J21">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2055,25 +2055,25 @@
         <v>30</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>26.7</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J22">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2087,25 +2087,25 @@
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F23">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>26.7</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2116,25 +2116,25 @@
         <v>440</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F24">
-        <v>440</v>
+        <v>121</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>27.5</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J24">
-        <v>440</v>
+        <v>40</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -2203,19 +2203,19 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H2" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I2" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2270,19 +2270,19 @@
         <v>42</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>78.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="H4" s="1">
-        <v>21.4</v>
+        <v>19</v>
       </c>
       <c r="I4" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2305,19 +2305,19 @@
         <v>39</v>
       </c>
       <c r="E5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>87.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>12.8</v>
+        <v>15.4</v>
       </c>
       <c r="I5" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2352,7 +2352,7 @@
         <v>20</v>
       </c>
       <c r="I6" s="2">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2375,19 +2375,19 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H7" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>94</v>
       </c>
       <c r="E8">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G8" s="1">
-        <v>81.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="H8" s="1">
-        <v>18.1</v>
+        <v>21.3</v>
       </c>
       <c r="I8" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v>43.6</v>
       </c>
       <c r="I9" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>7.1</v>
       </c>
       <c r="I10" s="2">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2512,19 +2512,19 @@
         <v>20</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2544,19 +2544,19 @@
         <v>87</v>
       </c>
       <c r="E12">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G12" s="1">
-        <v>78.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>21.8</v>
+        <v>24.1</v>
       </c>
       <c r="I12" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2614,19 +2614,19 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1">
-        <v>60</v>
+        <v>63.3</v>
       </c>
       <c r="H14" s="1">
-        <v>40</v>
+        <v>36.7</v>
       </c>
       <c r="I14" s="2">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2661,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2681,19 +2681,19 @@
         <v>86</v>
       </c>
       <c r="E16">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" s="1">
-        <v>83.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>16.3</v>
+        <v>15.1</v>
       </c>
       <c r="I16" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2751,19 +2751,19 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>96.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>3.6</v>
+        <v>7.1</v>
       </c>
       <c r="I18" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2786,19 +2786,19 @@
         <v>25</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G19" s="1">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H19" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I19" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2821,19 +2821,19 @@
         <v>20</v>
       </c>
       <c r="E20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H20" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2853,19 +2853,19 @@
         <v>101</v>
       </c>
       <c r="E21">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G21" s="1">
-        <v>89.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>10.9</v>
+        <v>13.9</v>
       </c>
       <c r="I21" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2888,16 +2888,16 @@
         <v>30</v>
       </c>
       <c r="E22">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G22" s="1">
-        <v>96.7</v>
+        <v>73.3</v>
       </c>
       <c r="H22" s="1">
-        <v>3.3</v>
+        <v>26.7</v>
       </c>
       <c r="I22" s="2">
         <v>7.5</v>
@@ -2920,16 +2920,16 @@
         <v>30</v>
       </c>
       <c r="E23">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G23" s="1">
-        <v>96.7</v>
+        <v>73.3</v>
       </c>
       <c r="H23" s="1">
-        <v>3.3</v>
+        <v>26.7</v>
       </c>
       <c r="I23" s="2">
         <v>7.5</v>
@@ -2949,19 +2949,19 @@
         <v>440</v>
       </c>
       <c r="E24">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="F24">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G24" s="1">
-        <v>83.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>16.1</v>
+        <v>19.1</v>
       </c>
       <c r="I24" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J24">
         <v>0</v>

--- a/academias/Programación - Estadisticos 20222.xlsx
+++ b/academias/Programación - Estadisticos 20222.xlsx
@@ -1746,25 +1746,25 @@
         <v>39</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F13">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>2.6</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J13">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1848,25 +1848,25 @@
         <v>86</v>
       </c>
       <c r="E16">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="F16">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1">
-        <v>41.9</v>
+        <v>86</v>
       </c>
       <c r="H16" s="1">
-        <v>58.1</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2">
-        <v>5.3</v>
+        <v>8.1</v>
       </c>
       <c r="J16">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>46.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2116,25 +2116,25 @@
         <v>440</v>
       </c>
       <c r="E24">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="F24">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="G24" s="1">
-        <v>72.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H24" s="1">
-        <v>27.5</v>
+        <v>18.9</v>
       </c>
       <c r="I24" s="2">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="J24">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K24" s="1">
-        <v>9.1</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2579,19 +2579,19 @@
         <v>39</v>
       </c>
       <c r="E13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>94.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="I13" s="2">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2681,19 +2681,19 @@
         <v>86</v>
       </c>
       <c r="E16">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1">
-        <v>84.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="H16" s="1">
-        <v>15.1</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2949,16 +2949,16 @@
         <v>440</v>
       </c>
       <c r="E24">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F24">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G24" s="1">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H24" s="1">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="I24" s="2">
         <v>7.6</v>

--- a/academias/Programación - Estadisticos 20222.xlsx
+++ b/academias/Programación - Estadisticos 20222.xlsx
@@ -1793,13 +1793,13 @@
         <v>36.7</v>
       </c>
       <c r="I14" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1863,10 +1863,10 @@
         <v>8.1</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2128,13 +2128,13 @@
         <v>18.9</v>
       </c>
       <c r="I24" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Programación - Estadisticos 20222.xlsx
+++ b/academias/Programación - Estadisticos 20222.xlsx
@@ -1314,8 +1314,7 @@
   <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -2147,8 +2146,7 @@
   <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -2203,19 +2201,19 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H2" s="1">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I2" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2238,19 +2236,19 @@
         <v>17</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I3" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2270,19 +2268,19 @@
         <v>42</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1">
-        <v>81</v>
+        <v>73.8</v>
       </c>
       <c r="H4" s="1">
-        <v>19</v>
+        <v>26.2</v>
       </c>
       <c r="I4" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2352,7 +2350,7 @@
         <v>20</v>
       </c>
       <c r="I6" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2375,19 +2373,19 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="H7" s="1">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I7" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2407,19 +2405,19 @@
         <v>94</v>
       </c>
       <c r="E8">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G8" s="1">
-        <v>78.7</v>
+        <v>75.5</v>
       </c>
       <c r="H8" s="1">
-        <v>21.3</v>
+        <v>24.5</v>
       </c>
       <c r="I8" s="2">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2477,19 +2475,19 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2512,16 +2510,16 @@
         <v>20</v>
       </c>
       <c r="E11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
         <v>7.6</v>
@@ -2544,16 +2542,16 @@
         <v>87</v>
       </c>
       <c r="E12">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F12">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G12" s="1">
-        <v>75.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="H12" s="1">
-        <v>24.1</v>
+        <v>20.7</v>
       </c>
       <c r="I12" s="2">
         <v>7.4</v>
@@ -2661,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2716,16 +2714,16 @@
         <v>28</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I17" s="2">
         <v>8.300000000000001</v>
@@ -2751,19 +2749,19 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="I18" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2786,19 +2784,19 @@
         <v>25</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19" s="1">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H19" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I19" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2833,7 +2831,7 @@
         <v>10</v>
       </c>
       <c r="I20" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2853,16 +2851,16 @@
         <v>101</v>
       </c>
       <c r="E21">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G21" s="1">
-        <v>86.09999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="I21" s="2">
         <v>7.9</v>
@@ -2949,19 +2947,19 @@
         <v>440</v>
       </c>
       <c r="E24">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F24">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G24" s="1">
-        <v>81.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="H24" s="1">
-        <v>18.9</v>
+        <v>19.8</v>
       </c>
       <c r="I24" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J24">
         <v>0</v>

--- a/academias/Programación - Estadisticos 20222.xlsx
+++ b/academias/Programación - Estadisticos 20222.xlsx
@@ -2577,19 +2577,19 @@
         <v>39</v>
       </c>
       <c r="E13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>97.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H13" s="1">
-        <v>2.6</v>
+        <v>7.7</v>
       </c>
       <c r="I13" s="2">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2612,19 +2612,19 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>63.3</v>
+        <v>86.7</v>
       </c>
       <c r="H14" s="1">
-        <v>36.7</v>
+        <v>13.3</v>
       </c>
       <c r="I14" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2679,19 +2679,19 @@
         <v>86</v>
       </c>
       <c r="E16">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F16">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G16" s="1">
-        <v>86</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>14</v>
+        <v>8.1</v>
       </c>
       <c r="I16" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2886,19 +2886,19 @@
         <v>30</v>
       </c>
       <c r="E22">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1">
-        <v>73.3</v>
+        <v>86.7</v>
       </c>
       <c r="H22" s="1">
-        <v>26.7</v>
+        <v>13.3</v>
       </c>
       <c r="I22" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2918,19 +2918,19 @@
         <v>30</v>
       </c>
       <c r="E23">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1">
-        <v>73.3</v>
+        <v>86.7</v>
       </c>
       <c r="H23" s="1">
-        <v>26.7</v>
+        <v>13.3</v>
       </c>
       <c r="I23" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -2947,16 +2947,16 @@
         <v>440</v>
       </c>
       <c r="E24">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="F24">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G24" s="1">
-        <v>80.2</v>
+        <v>82.3</v>
       </c>
       <c r="H24" s="1">
-        <v>19.8</v>
+        <v>17.7</v>
       </c>
       <c r="I24" s="2">
         <v>7.5</v>

--- a/academias/Programación - Estadisticos 20222.xlsx
+++ b/academias/Programación - Estadisticos 20222.xlsx
@@ -2303,19 +2303,19 @@
         <v>39</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>84.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="H5" s="1">
-        <v>15.4</v>
+        <v>12.8</v>
       </c>
       <c r="I5" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2373,16 +2373,16 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H7" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I7" s="2">
         <v>6.6</v>
@@ -2405,19 +2405,19 @@
         <v>94</v>
       </c>
       <c r="E8">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G8" s="1">
-        <v>75.5</v>
+        <v>77.7</v>
       </c>
       <c r="H8" s="1">
-        <v>24.5</v>
+        <v>22.3</v>
       </c>
       <c r="I8" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2440,19 +2440,19 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>56.4</v>
+        <v>87.2</v>
       </c>
       <c r="H9" s="1">
-        <v>43.6</v>
+        <v>12.8</v>
       </c>
       <c r="I9" s="2">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2542,19 +2542,19 @@
         <v>87</v>
       </c>
       <c r="E12">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>79.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>20.7</v>
+        <v>6.9</v>
       </c>
       <c r="I12" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2947,16 +2947,16 @@
         <v>440</v>
       </c>
       <c r="E24">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="F24">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G24" s="1">
-        <v>82.3</v>
+        <v>85.5</v>
       </c>
       <c r="H24" s="1">
-        <v>17.7</v>
+        <v>14.5</v>
       </c>
       <c r="I24" s="2">
         <v>7.5</v>
